--- a/solar-glow-drh-v2-BOM.xlsx
+++ b/solar-glow-drh-v2-BOM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="173">
   <si>
     <t xml:space="preserve">Quantity</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">MMSD301T1G</t>
   </si>
   <si>
-    <t xml:space="preserve">D1</t>
+    <t xml:space="preserve">D1, D9</t>
   </si>
   <si>
     <t xml:space="preserve">SM141K06TF</t>
@@ -84,19 +84,19 @@
     <t xml:space="preserve">C2, C3</t>
   </si>
   <si>
-    <t xml:space="preserve">CL10A105KP8NNNC</t>
+    <t xml:space="preserve">CL21A105KBCLNNC</t>
   </si>
   <si>
     <t xml:space="preserve">C4</t>
   </si>
   <si>
-    <t xml:space="preserve">GRM155R71H103KA88D</t>
+    <t xml:space="preserve">CL21B103KBANNNC</t>
   </si>
   <si>
     <t xml:space="preserve">C5</t>
   </si>
   <si>
-    <t xml:space="preserve">RC0402FR-071ML</t>
+    <t xml:space="preserve">RC0805FR-071ML</t>
   </si>
   <si>
     <t xml:space="preserve">R5, R6</t>
@@ -108,13 +108,10 @@
     <t xml:space="preserve">U3</t>
   </si>
   <si>
-    <t xml:space="preserve">GRM155R71C104KA88D</t>
-  </si>
-  <si>
     <t xml:space="preserve">C6</t>
   </si>
   <si>
-    <t xml:space="preserve">MMBT3906LT1G</t>
+    <t xml:space="preserve">BCP5316MTWG</t>
   </si>
   <si>
     <t xml:space="preserve">Q1</t>
@@ -126,19 +123,16 @@
     <t xml:space="preserve">U4</t>
   </si>
   <si>
-    <t xml:space="preserve">RC0402FR-0720KL</t>
+    <t xml:space="preserve">RC0805FR-071M8L</t>
   </si>
   <si>
     <t xml:space="preserve">R7</t>
   </si>
   <si>
-    <t xml:space="preserve">RC0402FR-0710KL</t>
-  </si>
-  <si>
     <t xml:space="preserve">R8</t>
   </si>
   <si>
-    <t xml:space="preserve">RC0402FR-071KL</t>
+    <t xml:space="preserve">RC0805FR-071KL</t>
   </si>
   <si>
     <t xml:space="preserve">R9</t>
@@ -147,19 +141,13 @@
     <t xml:space="preserve">C7</t>
   </si>
   <si>
-    <t xml:space="preserve">RC0402FR-074K7L</t>
+    <t xml:space="preserve">RC0805FR-074K7L</t>
   </si>
   <si>
     <t xml:space="preserve">R10, R11</t>
   </si>
   <si>
-    <t xml:space="preserve">PESD5V0S1BA,115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RC0402JR-070RL</t>
+    <t xml:space="preserve">RC0805JR-070RL</t>
   </si>
   <si>
     <t xml:space="preserve">SJ1</t>
@@ -222,7 +210,7 @@
     <t xml:space="preserve">STX = VQFN28. SSOP-28 (-I/SS) is the leaded option. FW: BODLEVEL ~2.6 V, PMODE=AUTO.</t>
   </si>
   <si>
-    <t xml:space="preserve">Solar blocking / charge diode (VIN-&gt;VS)</t>
+    <t xml:space="preserve">Solar blocking diode, one per panel (PV1-&gt;D1-&gt;VS, PV2-&gt;D9-&gt;VS)</t>
   </si>
   <si>
     <t xml:space="preserve">Schottky Vf~0.3-0.6 V</t>
@@ -237,6 +225,9 @@
     <t xml:space="preserve">MMSD301T1GOSCT-ND</t>
   </si>
   <si>
+    <t xml:space="preserve">D9 added v2 (per-panel: half-shade on one panel cannot back-drive the other through VS). Same part as D1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indoor solar cell x2 -- top + bottom thirds, wired parallel (charges the supercap stack)</t>
   </si>
   <si>
@@ -294,7 +285,7 @@
     <t xml:space="preserve">ALD910025SALI-ND</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormant at the clamped rail.</t>
+    <t xml:space="preserve">Dormant at the clamped rail. DS: ALD81-910025 (ALD810025-2.pdf, covers the SAL 8-pin dual; pin2=GN1,3=DN1,4=SN1 / 5=SN2/V-,6=DN2,7=GN2,8=V+,1=IC-&gt;V-).</t>
   </si>
   <si>
     <t xml:space="preserve">Glow LEDs -- reverse-mount through the FR4 DRH window</t>
@@ -345,6 +336,9 @@
     <t xml:space="preserve">1276-6557-1-ND</t>
   </si>
   <si>
+    <t xml:space="preserve">Order the -1- Cut Tape (1276-6557-1-ND); a BOM upload by MPN defaults to the -2- full reel (MOQ 4000, no qty-1 price). Same for C2/C3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCU VDD pin 24 + VDDIO2 decouple</t>
   </si>
   <si>
@@ -357,40 +351,28 @@
     <t xml:space="preserve">VS-rail bulk bypass</t>
   </si>
   <si>
-    <t xml:space="preserve">1 uF X5R 10 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1276-1182-1-ND</t>
+    <t xml:space="preserve">1 uF X5R 50 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(by MPN)</t>
   </si>
   <si>
     <t xml:space="preserve">CL05Y105KP6VPN, 0402 (v0 intent)</t>
   </si>
   <si>
-    <t xml:space="preserve">Switched to the 0603 part that matches the board land + is in stock; X5R is fine for a bypass.</t>
+    <t xml:space="preserve">Upsized 0603-&gt;0805 for hand-soldering (CL21A105KBCLNNC, 1uF 50V X5R, in stock); X5R is fine for a bypass. DS: CL21A105KBCLNNC Spec.pdf.</t>
   </si>
   <si>
     <t xml:space="preserve">VSENSE ADC filter (VSENSE-&gt;GND), RC with R5/R6 into PA5/AIN25</t>
   </si>
   <si>
-    <t xml:space="preserve">10 nF X7R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match by MPN</t>
+    <t xml:space="preserve">10 nF X7R 50 V</t>
   </si>
   <si>
     <t xml:space="preserve">— (added v1)</t>
   </si>
   <si>
-    <t xml:space="preserve">103 = 10 nF (the prior list matched a 39 nF by a wrong P/N).</t>
+    <t xml:space="preserve">103 = 10 nF. DigiKey-confirmed PN.</t>
   </si>
   <si>
     <t xml:space="preserve">Light-sense divider (VIN-&gt;VSENSE-&gt;GND)</t>
@@ -402,9 +384,6 @@
     <t xml:space="preserve">Yageo</t>
   </si>
   <si>
-    <t xml:space="preserve">311-1.00MLRCT-ND</t>
-  </si>
-  <si>
     <t xml:space="preserve">1M/1M -&gt; VSENSE ~= VIN/2 &lt; VDD.</t>
   </si>
   <si>
@@ -432,64 +411,61 @@
     <t xml:space="preserve">Accelerometer Vdd decouple</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1 uF X7R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">490-3261-1-ND</t>
-  </si>
-  <si>
     <t xml:space="preserve">— (added v2)</t>
   </si>
   <si>
     <t xml:space="preserve">Clamp PNP pass -- shunts VIN excess to GND (E-&gt;VIN, B-&gt;CLBASE, C-&gt;GND)</t>
   </si>
   <si>
-    <t xml:space="preserve">PNP 40 V 200 mA</t>
+    <t xml:space="preserve">PNP 80 V 1 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-WDFNW (2x2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DK# 25602738 (by MPN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCX53-16 / SOT-89 -- whole line went out of stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REWORK to WDFNW3 2x2 land (onsemi case 515AA). Wettable-flank DFN, deep stock, smaller than SOT-89 (eases the clamp cluster). Ptot 875 mW vs ~435 mW worst case -- about half its rating, comfortable. EXPOSED PAD = COLLECTOR -&gt; GND pour + a few thermal vias (heatsink, replaces the SOT-89 tab, and the collector tie, in one). Pins CONFIRMED from bcp53m-d.pdf (case 515AA, in repo): 1=Base-&gt;CLBASE, 2=Emitter-&gt;VIN, 3=Collector-&gt;GND -- B-E-C, NOT the SOT-223 BCP53 B-C-E (a guess would have swapped E/B). Pin 3 + exposed pad = same collector net -&gt; GND. Thermal Rth(j-a) 138 C/W @100 mm2 (Tj ~85 C at 435 mW), 78 C/W @600 mm2. DS: onsemi bcp53m-d.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp shunt reference 1.24 V (K-&gt;CLBASE, ref-&gt;CLREF, A-&gt;GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV431B, 1.24 V +/-0.5%</t>
   </si>
   <si>
     <t xml:space="preserve">SOT-23</t>
   </si>
   <si>
-    <t xml:space="preserve">MMBT3906LT1GOSCT-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The bare "MMBT3906" MPN hits an OBSOLETE part -- use the LT1G suffix. SOT-89 BCP53-16 if long bright-idle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp shunt reference 1.24 V (K-&gt;CLBASE, ref-&gt;CLREF, A-&gt;GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLV431B, 1.24 V +/-0.5%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Texas Instruments</t>
   </si>
   <si>
-    <t xml:space="preserve">Trip = 1.24x(1+R7/R8) = 3.72 V -&gt; VS ~= 3.42 V. (The prior P/N matched a TPD4E001 TVS array -- match by THIS MPN.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp divider top (VIN-&gt;CLREF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 kOhm +/-1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311-20.0KLRCT-ND</t>
+    <t xml:space="preserve">296-17569-1-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trip = 1.24x(1+R7/R8) = 1.24x2.8 = 3.47 V = VS clamp directly (clamp now sits on VS, not VIN -&gt; no Schottky-drop subtraction; under the accel 3.6 V rec max, well under 4.8 V abs max). SOT-23-3, +/-0.5%, 15 mA. DS: tlv431a-3.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp divider top (VS-&gt;CLREF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 MOhm +/-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-value vs old 20k: clamp on VS is always-on, so 1.8M/1M draws ~1.2 uA not ~120 uA (matters vs ~20 uA MCU sleep).</t>
   </si>
   <si>
     <t xml:space="preserve">Clamp divider bottom (CLREF-&gt;GND)</t>
   </si>
   <si>
-    <t xml:space="preserve">10 kOhm +/-1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311-10.0KLRCT-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp base pull-up / TLV431 cathode path (VIN-&gt;CLBASE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311-1.00KLRCT-ND</t>
+    <t xml:space="preserve">311-1.00MCRCT-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp base pull-up / TLV431 cathode path (VS-&gt;CLBASE)</t>
   </si>
   <si>
     <t xml:space="preserve">Clamp loop stability / local VIN bypass</t>
@@ -501,25 +477,7 @@
     <t xml:space="preserve">4.7 kOhm +/-1%</t>
   </si>
   <si>
-    <t xml:space="preserve">0402 (the prior list matched a 1206 by P/N). REQUIRED for the TWI bus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTN ESD clamp at the snap dome (BTN &lt;-&gt; GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 V bidir TVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD-323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexperia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1727-3837-1-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACKORDERED at DigiKey -- substitute any in-stock 5 V bidir SOD-323 ESD TVS (Bourns CDSOD323 / Littelfuse SD05 series).</t>
+    <t xml:space="preserve">0805 now (was 0402; the prior list matched a 1206 by P/N). REQUIRED for the TWI bus.</t>
   </si>
   <si>
     <t xml:space="preserve">VDDIO2 -&gt; VS tie</t>
@@ -528,7 +486,7 @@
     <t xml:space="preserve">0 Ohm jumper</t>
   </si>
   <si>
-    <t xml:space="preserve">0 Ohm 0402 or a solder bridge (no part). MUST be closed.</t>
+    <t xml:space="preserve">0 Ohm 0805 or a solder bridge (no part). MUST be closed.</t>
   </si>
   <si>
     <t xml:space="preserve">Per-board parts subtotal (indicative)</t>
@@ -549,7 +507,7 @@
     <t xml:space="preserve">Spot-check these three after upload:</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 = MMBT3906LT1G (the bare MMBT3906 is obsolete).   C4 = CL10A105KP8NNNC (1 uF 0603 -- swapped from the v0 0402 part to match the land + stock).   D8 = PESD5V0S1BA,115 is BACKORDERED -- pick any in-stock 5 V bidirectional SOD-323 ESD TVS.</t>
+    <t xml:space="preserve">Q1 = BCP5316MTWG / WDFNW3 2x2 (DK# 25602738) -- PNP; exposed pad = collector -&gt; GND pour + thermal vias (heatsink). Pins (bcp53m-d.pdf, case 515AA): 1=Base-&gt;CLBASE, 2=Emitter-&gt;VIN, 3=Collector-&gt;GND; pin 3 + exposed pad = collector -&gt; GND. C4 = CL21A105KBCLNNC (1 uF 50 V X5R 0805).</t>
   </si>
   <si>
     <t xml:space="preserve">Not purchased -- PCB / gerber features (no BOM line):</t>
@@ -570,7 +528,7 @@
     <t xml:space="preserve">Footprints:</t>
   </si>
   <si>
-    <t xml:space="preserve">Generator lands are placement placeholders. Set the real KiCad footprint per MPN: R1-4 1206 ; C1-3 0805 ; C4 0603 ; C5/C6/C7 0402 ; R5-R11 + SJ1 0402 ; U3 LGA-12 ; Q1/U4 SOT-23 ; D8 SOD-323 ; U2 SOIC-8 ; U1 VQFN28.</t>
+    <t xml:space="preserve">Generator lands are placement placeholders. Set the real KiCad footprint per MPN: R1-4 1206 ; C1-7 0805 ; R5-R11 + SJ1 0805 ; U3 LGA-12 ; U4 SOT-23 ; Q1 WDFNW3 2x2 (exposed pad=collector) ; U2 SOIC-8 ; U1 VQFN28.</t>
   </si>
   <si>
     <t xml:space="preserve">Firmware / build must-dos:</t>
@@ -593,7 +551,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,14 +606,6 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF7F6000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -751,7 +701,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -784,23 +734,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,7 +754,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1064,7 +1010,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1096,7 +1042,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1231,10 +1177,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1242,10 +1188,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1253,10 +1199,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,10 +1210,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1275,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1286,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1297,10 +1243,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1308,10 +1254,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1319,21 +1265,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1287,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -1370,40 +1305,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1414,22 +1349,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>1.17</v>
@@ -1439,48 +1374,50 @@
         <v>1.17</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="J3" s="6" t="n">
         <f aca="false">B3*I3</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -1490,22 +1427,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>7.61</v>
@@ -1515,10 +1452,10 @@
         <v>15.22</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,22 +1466,22 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>16.69</v>
@@ -1554,13 +1491,13 @@
         <v>66.76</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -1568,22 +1505,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>7.68</v>
@@ -1593,10 +1530,10 @@
         <v>7.68</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,22 +1544,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.27</v>
@@ -1632,10 +1569,10 @@
         <v>1.08</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1646,22 +1583,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0.47</v>
@@ -1671,11 +1608,11 @@
         <v>1.88</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1683,22 +1620,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.22</v>
@@ -1708,9 +1645,11 @@
         <v>0.22</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -1720,22 +1659,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.22</v>
@@ -1745,13 +1684,13 @@
         <v>0.44</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1759,22 +1698,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.1</v>
@@ -1784,10 +1723,10 @@
         <v>0.1</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1798,22 +1737,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>120</v>
+      <c r="H12" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0.1</v>
@@ -1823,10 +1762,10 @@
         <v>0.1</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1837,22 +1776,22 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.1</v>
@@ -1862,10 +1801,10 @@
         <v>0.2</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1876,22 +1815,22 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1.79</v>
@@ -1901,151 +1840,151 @@
         <v>1.79</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J15" s="6" t="n">
         <f aca="false">B15*I15</f>
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="6" t="n">
         <f aca="false">B16*I16</f>
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="K16" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>120</v>
+        <v>31</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4</v>
+        <v>0.84</v>
       </c>
       <c r="J17" s="6" t="n">
         <f aca="false">B17*I17</f>
-        <v>0.4</v>
+        <v>0.84</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.1</v>
@@ -2055,34 +1994,36 @@
         <v>0.1</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="L18" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.1</v>
@@ -2092,34 +2033,34 @@
         <v>0.1</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.1</v>
@@ -2129,71 +2070,71 @@
         <v>0.1</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J21" s="6" t="n">
         <f aca="false">B21*I21</f>
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>120</v>
+        <v>39</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.1</v>
@@ -2203,108 +2144,69 @@
         <v>0.2</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J23" s="6" t="n">
         <f aca="false">B23*I23</f>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <f aca="false">B24*I24</f>
-        <v>0.1</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="11" t="n">
-        <f aca="false">SUM(J2:J24)</f>
-        <v>98.49</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="10" t="n">
+        <f aca="false">SUM(J2:J23)</f>
+        <v>99.32</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2329,109 +2231,109 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/solar-glow-drh-v2-BOM.xlsx
+++ b/solar-glow-drh-v2-BOM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="184">
   <si>
     <t xml:space="preserve">Quantity</t>
   </si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">D2, D3, D4, D5</t>
   </si>
   <si>
-    <t xml:space="preserve">TNPW12061K00FEEA</t>
+    <t xml:space="preserve">TNPW1206150RFEEA</t>
   </si>
   <si>
     <t xml:space="preserve">R1, R2, R3, R4</t>
@@ -153,6 +153,18 @@
     <t xml:space="preserve">SJ1</t>
   </si>
   <si>
+    <t xml:space="preserve">RC0805FR-07220RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref(s)</t>
   </si>
   <si>
@@ -309,165 +321,168 @@
     <t xml:space="preserve">LED ballast -- one per LED, per-LED low-side PWM</t>
   </si>
   <si>
+    <t xml:space="preserve">150 Ohm +/-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishay Dale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(by MPN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA P47F: VF 2.05V typ @30mA, IF max 50mA. VS clamped &lt;=3.47V, so 150R -&gt; ~4-10mA per LED (visible amber, ~30pct of 30mA brightness, ~40s on 4 LEDs off-sun). Old 1k gave only ~1mA (too dim, mismatched the runtime note). Lower R = brighter+shorter; higher = dimmer+longer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCU VDD decouple (pin 18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 uF X7R 50 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1276-6557-1-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order the -1- Cut Tape (1276-6557-1-ND); a BOM upload by MPN defaults to the -2- full reel (MOQ 4000, no qty-1 price). Same for C2/C3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCU VDD pin 24 + VDDIO2 decouple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 uF CL21B105KBFVPNE (v0 VS-bypass)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role reassigned to per-pin decoupling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS-rail bulk bypass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 uF X5R 50 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL05Y105KP6VPN, 0402 (v0 intent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upsized 0603-&gt;0805 for hand-soldering (CL21A105KBCLNNC, 1uF 50V X5R, in stock); X5R is fine for a bypass. DS: CL21A105KBCLNNC Spec.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSENSE ADC filter (VSENSE-&gt;GND), RC with R5/R6 into PA5/AIN25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 nF X7R 50 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (added v1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103 = 10 nF. DigiKey-confirmed PN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light-sense divider (VIN-&gt;VSENSE-&gt;GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 MOhm +/-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yageo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1M/1M -&gt; VSENSE ~= VIN/2 &lt; VDD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accelerometer -- tap / wake on I2C (INT1-&gt;PF1, INT2-&gt;PF0, addr 0x18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/-2-16 g, 1.71-3.6 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGA-12 2x2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STMicroelectronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">497-14851-1-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 keepout reservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6 V max -&gt; the VS clamp keeps VS ~= 3.42 V (no LDO).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accelerometer Vdd decouple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (added v2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp PNP pass -- shunts VIN excess to GND (E-&gt;VIN, B-&gt;CLBASE, C-&gt;GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNP 80 V 1 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-WDFNW (2x2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DK# 25602738 (by MPN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCX53-16 / SOT-89 -- whole line went out of stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REWORK to WDFNW3 2x2 land (onsemi case 515AA). Wettable-flank DFN, deep stock, smaller than SOT-89 (eases the clamp cluster). Ptot 875 mW vs ~435 mW worst case -- about half its rating, comfortable. EXPOSED PAD = COLLECTOR -&gt; GND pour + a few thermal vias (heatsink, replaces the SOT-89 tab, and the collector tie, in one). Pins CONFIRMED from bcp53m-d.pdf (case 515AA, in repo): 1=Base-&gt;CLBASE, 2=Emitter-&gt;VIN, 3=Collector-&gt;GND -- B-E-C, NOT the SOT-223 BCP53 B-C-E (a guess would have swapped E/B). Pin 3 + exposed pad = same collector net -&gt; GND. Thermal Rth(j-a) 138 C/W @100 mm2 (Tj ~85 C at 435 mW), 78 C/W @600 mm2. DS: onsemi bcp53m-d.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp shunt reference 1.24 V (K-&gt;CLBASE, ref-&gt;CLREF, A-&gt;GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV431B, 1.24 V +/-0.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas Instruments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">296-17569-1-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trip = 1.24x(1+R7/R8) = 1.24x2.8 = 3.47 V = VS clamp directly (clamp now sits on VS, not VIN -&gt; no Schottky-drop subtraction; under the accel 3.6 V rec max, well under 4.8 V abs max). SOT-23-3, +/-0.5%, 15 mA. DS: tlv431a-3.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp divider top (VS-&gt;CLREF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 MOhm +/-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-value vs old 20k: clamp on VS is always-on, so 1.8M/1M draws ~1.2 uA not ~120 uA (matters vs ~20 uA MCU sleep).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp divider bottom (CLREF-&gt;GND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311-1.00MCRCT-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamp base pull-up / TLV431 cathode path (VS-&gt;CLBASE)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 kOhm +/-1%</t>
   </si>
   <si>
-    <t xml:space="preserve">1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vishay Dale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">541-TNPW12061K00FEEACT-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCU VDD decouple (pin 18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1 uF X7R 50 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1276-6557-1-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order the -1- Cut Tape (1276-6557-1-ND); a BOM upload by MPN defaults to the -2- full reel (MOQ 4000, no qty-1 price). Same for C2/C3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCU VDD pin 24 + VDDIO2 decouple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 uF CL21B105KBFVPNE (v0 VS-bypass)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role reassigned to per-pin decoupling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS-rail bulk bypass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 uF X5R 50 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(by MPN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL05Y105KP6VPN, 0402 (v0 intent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upsized 0603-&gt;0805 for hand-soldering (CL21A105KBCLNNC, 1uF 50V X5R, in stock); X5R is fine for a bypass. DS: CL21A105KBCLNNC Spec.pdf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSENSE ADC filter (VSENSE-&gt;GND), RC with R5/R6 into PA5/AIN25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 nF X7R 50 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— (added v1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103 = 10 nF. DigiKey-confirmed PN.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light-sense divider (VIN-&gt;VSENSE-&gt;GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 MOhm +/-1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yageo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1M/1M -&gt; VSENSE ~= VIN/2 &lt; VDD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accelerometer -- tap / wake on I2C (INT1-&gt;PF1, INT2-&gt;PF0, addr 0x18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/-2-16 g, 1.71-3.6 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGA-12 2x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STMicroelectronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">497-14851-1-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 keepout reservation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6 V max -&gt; the VS clamp keeps VS ~= 3.42 V (no LDO).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accelerometer Vdd decouple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— (added v2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp PNP pass -- shunts VIN excess to GND (E-&gt;VIN, B-&gt;CLBASE, C-&gt;GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNP 80 V 1 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-WDFNW (2x2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DK# 25602738 (by MPN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCX53-16 / SOT-89 -- whole line went out of stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REWORK to WDFNW3 2x2 land (onsemi case 515AA). Wettable-flank DFN, deep stock, smaller than SOT-89 (eases the clamp cluster). Ptot 875 mW vs ~435 mW worst case -- about half its rating, comfortable. EXPOSED PAD = COLLECTOR -&gt; GND pour + a few thermal vias (heatsink, replaces the SOT-89 tab, and the collector tie, in one). Pins CONFIRMED from bcp53m-d.pdf (case 515AA, in repo): 1=Base-&gt;CLBASE, 2=Emitter-&gt;VIN, 3=Collector-&gt;GND -- B-E-C, NOT the SOT-223 BCP53 B-C-E (a guess would have swapped E/B). Pin 3 + exposed pad = same collector net -&gt; GND. Thermal Rth(j-a) 138 C/W @100 mm2 (Tj ~85 C at 435 mW), 78 C/W @600 mm2. DS: onsemi bcp53m-d.pdf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp shunt reference 1.24 V (K-&gt;CLBASE, ref-&gt;CLREF, A-&gt;GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLV431B, 1.24 V +/-0.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas Instruments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">296-17569-1-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trip = 1.24x(1+R7/R8) = 1.24x2.8 = 3.47 V = VS clamp directly (clamp now sits on VS, not VIN -&gt; no Schottky-drop subtraction; under the accel 3.6 V rec max, well under 4.8 V abs max). SOT-23-3, +/-0.5%, 15 mA. DS: tlv431a-3.pdf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp divider top (VS-&gt;CLREF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8 MOhm +/-1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High-value vs old 20k: clamp on VS is always-on, so 1.8M/1M draws ~1.2 uA not ~120 uA (matters vs ~20 uA MCU sleep).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp divider bottom (CLREF-&gt;GND)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311-1.00MCRCT-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clamp base pull-up / TLV431 cathode path (VS-&gt;CLBASE)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clamp loop stability / local VIN bypass</t>
   </si>
   <si>
@@ -489,6 +504,24 @@
     <t xml:space="preserve">0 Ohm 0805 or a solder bridge (no part). MUST be closed.</t>
   </si>
   <si>
+    <t xml:space="preserve">TINY-mode LED dim ballast (ANODE common -&gt; VS via SW2 TINY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 Ohm +/-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With R1-4=150R, R12=220R (shared by 4 anodes) -&gt; ~1.6mA per LED in TINY, about 6x dimmer than ON (~4min on 4 LEDs off-sun). Brightness scales with how many LEDs are lit. Tune to taste.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED master selector (OFF / ON / TINY) -- 3-pad solder bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-pad solder bridge (no part)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center pad = ANODE common. Bridge center-ON = anodes to VS; center-TINY = anodes via R12 (dim); unbridged = OFF (true hardware off, supercap-safe for storage).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Per-board parts subtotal (indicative)</t>
   </si>
   <si>
@@ -513,7 +546,7 @@
     <t xml:space="preserve">Not purchased -- PCB / gerber features (no BOM line):</t>
   </si>
   <si>
-    <t xml:space="preserve">SB1-4 per-LED test solder bridges ; J1 bare UPDI pads ; JP1 I2C breakout ; JP2 spare-GPIO breakout ; MH1-4 M2 mounting holes ; TC1 Tag-Connect TC2030 land.</t>
+    <t xml:space="preserve">SB1-4 per-LED force-on jumpers (bridge LDRVn-&gt;GND = that LED on without the MCU; pairs with SW2 master OFF/ON/TINY) ; J1 bare UPDI pads ; JP1 I2C breakout ; JP2 spare-GPIO breakout ; MH1-4 M2 mounting holes ; TC1 Tag-Connect TC2030 land.</t>
   </si>
   <si>
     <t xml:space="preserve">Programming tools (one-time): a TC2030-IDC-NL no-legs cable + a USB-serial UPDI adapter. NOT the TC2030-MCP cable (PIC-only).</t>
@@ -528,7 +561,7 @@
     <t xml:space="preserve">Footprints:</t>
   </si>
   <si>
-    <t xml:space="preserve">Generator lands are placement placeholders. Set the real KiCad footprint per MPN: R1-4 1206 ; C1-7 0805 ; R5-R11 + SJ1 0805 ; U3 LGA-12 ; U4 SOT-23 ; Q1 WDFNW3 2x2 (exposed pad=collector) ; U2 SOIC-8 ; U1 VQFN28.</t>
+    <t xml:space="preserve">Generator lands are placement placeholders. Set the real KiCad footprint per MPN: R1-4 1206 ; C1-7 0805 ; R5-R12 + SJ1 0805 ; SW2 3-pad solder bridge ; U3 LGA-12 ; U4 SOT-23 ; Q1 WDFNW3 2x2 (exposed pad=collector) ; U2 SOIC-8 ; U1 VQFN28.</t>
   </si>
   <si>
     <t xml:space="preserve">Firmware / build must-dos:</t>
@@ -1010,7 +1043,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1269,6 +1302,28 @@
       </c>
       <c r="C23" s="2" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1287,7 +1342,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -1305,40 +1360,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1349,22 +1404,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>1.17</v>
@@ -1374,10 +1429,10 @@
         <v>1.17</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1388,22 +1443,22 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.2</v>
@@ -1413,10 +1468,10 @@
         <v>0.4</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1427,22 +1482,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>7.61</v>
@@ -1452,10 +1507,10 @@
         <v>15.22</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1466,22 +1521,22 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>16.69</v>
@@ -1491,10 +1546,10 @@
         <v>66.76</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1505,22 +1560,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>7.68</v>
@@ -1530,10 +1585,10 @@
         <v>7.68</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1544,22 +1599,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.27</v>
@@ -1569,13 +1624,13 @@
         <v>1.08</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -1583,22 +1638,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0.47</v>
@@ -1608,9 +1663,11 @@
         <v>1.88</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -1620,22 +1677,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.22</v>
@@ -1645,10 +1702,10 @@
         <v>0.22</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1659,22 +1716,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0.22</v>
@@ -1684,10 +1741,10 @@
         <v>0.44</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1698,22 +1755,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.1</v>
@@ -1723,10 +1780,10 @@
         <v>0.1</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1737,22 +1794,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0.1</v>
@@ -1762,10 +1819,10 @@
         <v>0.1</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1776,22 +1833,22 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.1</v>
@@ -1801,10 +1858,10 @@
         <v>0.2</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1815,22 +1872,22 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1.79</v>
@@ -1840,10 +1897,10 @@
         <v>1.79</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1854,22 +1911,22 @@
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.22</v>
@@ -1879,7 +1936,7 @@
         <v>0.22</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L15" s="5"/>
     </row>
@@ -1891,22 +1948,22 @@
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0.4</v>
@@ -1916,10 +1973,10 @@
         <v>0.4</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1930,22 +1987,22 @@
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.84</v>
@@ -1955,10 +2012,10 @@
         <v>0.84</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,22 +2026,22 @@
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.1</v>
@@ -1994,10 +2051,10 @@
         <v>0.1</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2008,22 +2065,22 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.1</v>
@@ -2033,7 +2090,7 @@
         <v>0.1</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L19" s="5"/>
     </row>
@@ -2045,22 +2102,22 @@
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.1</v>
@@ -2070,7 +2127,7 @@
         <v>0.1</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L20" s="5"/>
     </row>
@@ -2082,22 +2139,22 @@
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.22</v>
@@ -2107,7 +2164,7 @@
         <v>0.22</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L21" s="5"/>
     </row>
@@ -2119,22 +2176,22 @@
         <v>2</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.1</v>
@@ -2144,10 +2201,10 @@
         <v>0.2</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2158,22 +2215,22 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>41</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.1</v>
@@ -2183,30 +2240,108 @@
         <v>0.1</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="10" t="n">
-        <f aca="false">SUM(J2:J23)</f>
-        <v>99.32</v>
-      </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <f aca="false">B24*I24</f>
+        <v>0.1</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <f aca="false">B25*I25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="10" t="n">
+        <f aca="false">SUM(J2:J25)</f>
+        <v>99.42</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2232,7 +2367,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2240,17 +2375,17 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2258,12 +2393,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2271,17 +2406,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2289,12 +2424,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2302,12 +2437,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2315,12 +2450,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2328,12 +2463,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/solar-glow-drh-v2-BOM.xlsx
+++ b/solar-glow-drh-v2-BOM.xlsx
@@ -546,7 +546,7 @@
     <t xml:space="preserve">Not purchased -- PCB / gerber features (no BOM line):</t>
   </si>
   <si>
-    <t xml:space="preserve">SB1-4 per-LED force-on jumpers (bridge LDRVn-&gt;GND = that LED on without the MCU; pairs with SW2 master OFF/ON/TINY) ; J1 bare UPDI pads ; JP1 I2C breakout ; JP2 spare-GPIO breakout ; MH1-4 M2 mounting holes ; TC1 Tag-Connect TC2030 land.</t>
+    <t xml:space="preserve">SB1-4 per-LED force-on jumpers (bridge LDRVn-&gt;GND = that LED on without the MCU; pairs with SW2 master OFF/ON/TINY) ; J1 bare UPDI pads ; JP1 I2C breakout ; JP2 spare-GPIO breakout ; MH1-4 M2 mounting holes ; TC1 Tag-Connect TC2030 legged land, DNL (board has only the footprint). Position LOCKED under SC1 = program the bare board, mount caps last. Footprint TC2030-MCP-FP: 6 contact pads dia 0.787mm NO mask NO paste on 1.27mm grid (1=UPDI,2=VS,3=GND,4-6 NC) + 3 alignment holes dia 0.991 + 4 leg-latch holes dia 2.375 (the 4 clipping points; may be plated per note 5 to carry VS/GND). Geometry = official KiCad Tag-Connect TC2030-IDC-FP footprint.</t>
   </si>
   <si>
     <t xml:space="preserve">Programming tools (one-time): a TC2030-IDC-NL no-legs cable + a USB-serial UPDI adapter. NOT the TC2030-MCP cable (PIC-only).</t>
